--- a/2026_09_15/requests list.xlsx
+++ b/2026_09_15/requests list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimmylam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_09_15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98E0A15-8471-4937-9E78-C584F5949E87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA32EFC-408A-4484-B8BE-23F6CB5DFFD6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7950" windowHeight="8730" xr2:uid="{9D5F5BEC-49D0-48F4-983E-B88FCE20EBFD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>1. Email Lists for Travel eDM (Jessie Pang)</t>
   </si>
@@ -34,39 +34,6 @@
   </si>
   <si>
     <t>2. Data for Media Kit (Lily)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 
-DECLARE @start_date DATE = '2026-07-01';
-DECLARE @end_date DATE = '2026-07-31';
- use mars
- ---- Total unique users ever booked 
-Select COUNT(DISTINCT CAST(UserId AS nvarchar(20)) + CAST(DinerPhone_Hash AS nvarchar(30)))
-FROM [Booking] (nolock) B
-WHERE BookingTime &lt; @end_date
- AND Source IN (1, 4, 5, 6, 7, 9, 11, 12, 13, 21, 25, 26, 27, 28, 29, 30) 
- ---- Average Daily Bookings 
-SELECT count(bookingid)/datediff(day, @start_date, @end_date) from booking b (nolock)
-left join poi p (nolock) on b.poiid = p.poiid
-where p.status not in (2,6) 
-and bookingtime&gt;=@start_date and bookingtime&lt;@end_date
-and b.status =10
- AND Source IN (1, 4, 5, 6, 7, 9, 11, 12, 13, 21, 25, 26, 27, 28, 29, 30) 
-use openrice3
----- Asia Miles Bound Accounts 
-SELECT COUNT(DISTINCT UserId) FROM UserIM WHERE 
-IMTypeId IN (30, 31)
-AND ModifyTime &lt; @end_date
---- HK - MAU
-SELECT count(distinct UserDeviceId) from UserDevice 
-WHERE convert(Date, ModifyTime) between @start_date and @end_date
---- bind card
-use mars;
-Select
-count(distinct SSOuserID) as user_count
-FROM UserCreditCard_BA
-WHERE convert(date, CreateTime)&lt;=@end_date and status=10
-</t>
   </si>
   <si>
     <t>http://172.17.2.220:8888/notebooks/KimmyLam/20250925_adhocData/oversea_bookmark_count.ipynb</t>
@@ -151,6 +118,42 @@
   </si>
   <si>
     <t>scheduled in airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+DECLARE @start_date DATE = '2026-07-01';
+DECLARE @end_date DATE = '2026-07-31';
+ use mars
+ ----1.  Total unique users ever booked 
+Select COUNT(DISTINCT CAST(UserId AS nvarchar(20)) + CAST(DinerPhone_Hash AS nvarchar(30)))
+FROM [Booking] (nolock) B
+WHERE BookingTime &lt; @end_date
+ AND Source IN (1, 4, 5, 6, 7, 9, 11, 12, 13, 21, 25, 26, 27, 28, 29, 30) 
+ ----2.  Average Daily Bookings 
+SELECT count(bookingid)/datediff(day, @start_date, @end_date) from booking b (nolock)
+left join poi p (nolock) on b.poiid = p.poiid
+where p.status not in (2,6) 
+and bookingtime&gt;=@start_date and bookingtime&lt;@end_date
+and b.status =10
+ AND Source IN (1, 4, 5, 6, 7, 9, 11, 12, 13, 21, 25, 26, 27, 28, 29, 30) 
+use openrice3
+----3. Asia Miles Bound Accounts 
+SELECT COUNT(DISTINCT UserId) FROM UserIM WHERE 
+IMTypeId IN (30, 31)
+AND ModifyTime &lt; @end_date
+--- 7. HK - MAU
+SELECT count(distinct UserDeviceId) from UserDevice 
+WHERE convert(Date, ModifyTime) between @start_date and @end_date
+--- 8. bind card
+use mars;
+Select
+count(distinct SSOuserID) as user_count
+FROM UserCreditCard_BA
+WHERE convert(date, CreateTime)&lt;=@end_date and status=10
+</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -548,28 +551,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="297.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="7">
-        <v>3</v>
+      <c r="B6" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,53 +580,53 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -631,32 +634,32 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/2026_09_15/requests list.xlsx
+++ b/2026_09_15/requests list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_09_15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA32EFC-408A-4484-B8BE-23F6CB5DFFD6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6868E6-F223-4167-A940-BECF32FE94F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7950" windowHeight="8730" xr2:uid="{9D5F5BEC-49D0-48F4-983E-B88FCE20EBFD}"/>
   </bookViews>
